--- a/data/druga-mila.xlsx
+++ b/data/druga-mila.xlsx
@@ -870,7 +870,7 @@
         <v>BLUE CARGO</v>
       </c>
       <c r="C28" t="str">
-        <v>54-028 Wrocław Rajska 3</v>
+        <v>Jesionowa 20 55-095 Bąków</v>
       </c>
       <c r="D28" t="str">
         <v>PLAC</v>
